--- a/tests/moto/resultats/missions-e2e.xlsx
+++ b/tests/moto/resultats/missions-e2e.xlsx
@@ -454,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T12:28:34.943+00:00</v>
+        <v>2026-11-01T12:49:20.578+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T12:28:31.443+00:00</v>
+        <v>2026-11-01T12:49:17.178+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -519,7 +519,7 @@
         <v>Lu, confirmé</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-11-01T12:28:33.233+00:00</v>
+        <v>2026-11-01T12:49:18.928+00:00</v>
       </c>
       <c r="J3">
         <v>343</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T12:28:34.943+00:00</v>
+        <v>2026-11-01T12:49:20.578+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T12:28:31.443+00:00</v>
+        <v>2026-11-01T12:49:17.178+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>

--- a/tests/moto/resultats/missions-e2e.xlsx
+++ b/tests/moto/resultats/missions-e2e.xlsx
@@ -454,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T12:49:20.578+00:00</v>
+        <v>2026-11-01T13:00:20.633+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T12:49:17.178+00:00</v>
+        <v>2026-11-01T13:00:17.353+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -519,7 +519,7 @@
         <v>Lu, confirmé</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-11-01T12:49:18.928+00:00</v>
+        <v>2026-11-01T13:00:19.052+00:00</v>
       </c>
       <c r="J3">
         <v>343</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T12:49:20.578+00:00</v>
+        <v>2026-11-01T13:00:20.633+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T12:49:17.178+00:00</v>
+        <v>2026-11-01T13:00:17.353+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>

--- a/tests/moto/resultats/missions-e2e.xlsx
+++ b/tests/moto/resultats/missions-e2e.xlsx
@@ -454,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T13:00:20.633+00:00</v>
+        <v>2026-11-01T13:10:50.708+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T13:00:17.353+00:00</v>
+        <v>2026-11-01T13:10:47.473+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -519,7 +519,7 @@
         <v>Lu, confirmé</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-11-01T13:00:19.052+00:00</v>
+        <v>2026-11-01T13:10:49.124+00:00</v>
       </c>
       <c r="J3">
         <v>343</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T13:00:20.633+00:00</v>
+        <v>2026-11-01T13:10:50.708+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T13:00:17.353+00:00</v>
+        <v>2026-11-01T13:10:47.473+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>

--- a/tests/moto/resultats/missions-e2e.xlsx
+++ b/tests/moto/resultats/missions-e2e.xlsx
@@ -454,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T13:10:50.708+00:00</v>
+        <v>2026-11-01T13:16:45.86+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T13:10:47.473+00:00</v>
+        <v>2026-11-01T13:16:42.378+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -519,7 +519,7 @@
         <v>Lu, confirmé</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-11-01T13:10:49.124+00:00</v>
+        <v>2026-11-01T13:16:44.144+00:00</v>
       </c>
       <c r="J3">
         <v>343</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-11-01T13:10:50.708+00:00</v>
+        <v>2026-11-01T13:16:45.86+00:00</v>
       </c>
       <c r="B2" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-11-01T13:10:47.473+00:00</v>
+        <v>2026-11-01T13:16:42.378+00:00</v>
       </c>
       <c r="B3" t="str">
         <v>UH SAKASSOU E2E FICTIF</v>
